--- a/artfynd/A 22554-2024 artfynd.xlsx
+++ b/artfynd/A 22554-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118393904</v>
+        <v>118394590</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,45 +793,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511906</v>
+        <v>511742</v>
       </c>
       <c r="R3" t="n">
-        <v>6984171</v>
+        <v>6984146</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,9 +859,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,7 +898,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118393781</v>
+        <v>118393904</v>
       </c>
       <c r="B4" t="n">
         <v>97846</v>
@@ -922,12 +933,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -936,13 +942,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511873</v>
+        <v>511906</v>
       </c>
       <c r="R4" t="n">
-        <v>6984099</v>
+        <v>6984171</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,19 +975,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118394590</v>
+        <v>118393781</v>
       </c>
       <c r="B5" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,43 +1016,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511742</v>
+        <v>511873</v>
       </c>
       <c r="R5" t="n">
-        <v>6984146</v>
+        <v>6984099</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1783,10 +1783,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118393044</v>
+        <v>118394693</v>
       </c>
       <c r="B12" t="n">
-        <v>82263</v>
+        <v>57290</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1799,34 +1799,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511724</v>
+        <v>511716</v>
       </c>
       <c r="R12" t="n">
-        <v>6984047</v>
+        <v>6984145</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,10 +1890,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118394693</v>
+        <v>118393044</v>
       </c>
       <c r="B13" t="n">
-        <v>57290</v>
+        <v>82263</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1901,39 +1906,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511716</v>
+        <v>511724</v>
       </c>
       <c r="R13" t="n">
-        <v>6984145</v>
+        <v>6984047</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -3331,10 +3331,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118394901</v>
+        <v>118393935</v>
       </c>
       <c r="B26" t="n">
-        <v>57290</v>
+        <v>82263</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3347,42 +3347,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511694</v>
+        <v>511922</v>
       </c>
       <c r="R26" t="n">
-        <v>6984128</v>
+        <v>6984163</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3409,19 +3404,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3448,10 +3433,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118393935</v>
+        <v>118394248</v>
       </c>
       <c r="B27" t="n">
-        <v>82263</v>
+        <v>90504</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3464,21 +3449,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3488,10 +3473,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511922</v>
+        <v>511950</v>
       </c>
       <c r="R27" t="n">
-        <v>6984163</v>
+        <v>6984198</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3550,7 +3535,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118394248</v>
+        <v>118394327</v>
       </c>
       <c r="B28" t="n">
         <v>90504</v>
@@ -3590,13 +3575,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>511950</v>
+        <v>511917</v>
       </c>
       <c r="R28" t="n">
-        <v>6984198</v>
+        <v>6984200</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3623,9 +3608,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3652,10 +3647,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118394327</v>
+        <v>118393472</v>
       </c>
       <c r="B29" t="n">
-        <v>90504</v>
+        <v>97846</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3664,41 +3659,45 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511917</v>
+        <v>511752</v>
       </c>
       <c r="R29" t="n">
-        <v>6984200</v>
+        <v>6984084</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3725,19 +3724,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3764,10 +3753,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118393626</v>
+        <v>118395030</v>
       </c>
       <c r="B30" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3776,43 +3765,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511824</v>
+        <v>511734</v>
       </c>
       <c r="R30" t="n">
-        <v>6984090</v>
+        <v>6984117</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3871,10 +3855,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118394207</v>
+        <v>118394298</v>
       </c>
       <c r="B31" t="n">
-        <v>74596</v>
+        <v>97846</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3883,41 +3867,45 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>511968</v>
+        <v>511911</v>
       </c>
       <c r="R31" t="n">
-        <v>6984167</v>
+        <v>6984196</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3944,19 +3932,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3983,10 +3961,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118393472</v>
+        <v>118394901</v>
       </c>
       <c r="B32" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3995,30 +3973,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4027,13 +4006,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>511752</v>
+        <v>511694</v>
       </c>
       <c r="R32" t="n">
-        <v>6984084</v>
+        <v>6984128</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4060,9 +4039,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4089,10 +4078,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118395030</v>
+        <v>118393626</v>
       </c>
       <c r="B33" t="n">
-        <v>97846</v>
+        <v>78484</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4101,38 +4090,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>511734</v>
+        <v>511824</v>
       </c>
       <c r="R33" t="n">
-        <v>6984117</v>
+        <v>6984090</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4191,10 +4185,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118394298</v>
+        <v>118394207</v>
       </c>
       <c r="B34" t="n">
-        <v>97846</v>
+        <v>74596</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4203,45 +4197,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>511911</v>
+        <v>511968</v>
       </c>
       <c r="R34" t="n">
-        <v>6984196</v>
+        <v>6984167</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4268,9 +4258,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5191,10 +5191,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118394030</v>
+        <v>118394417</v>
       </c>
       <c r="B43" t="n">
-        <v>90504</v>
+        <v>97846</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5203,41 +5203,50 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>512003</v>
+        <v>511856</v>
       </c>
       <c r="R43" t="n">
-        <v>6984152</v>
+        <v>6984192</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5264,9 +5273,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5293,10 +5312,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118394417</v>
+        <v>118394030</v>
       </c>
       <c r="B44" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5305,50 +5324,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>511856</v>
+        <v>512003</v>
       </c>
       <c r="R44" t="n">
-        <v>6984192</v>
+        <v>6984152</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5375,19 +5385,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5521,10 +5521,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118393897</v>
+        <v>118393885</v>
       </c>
       <c r="B46" t="n">
-        <v>82263</v>
+        <v>97846</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5533,38 +5533,42 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>511911</v>
+        <v>511892</v>
       </c>
       <c r="R46" t="n">
-        <v>6984171</v>
+        <v>6984185</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5623,10 +5627,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118393821</v>
+        <v>118393746</v>
       </c>
       <c r="B47" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5635,25 +5639,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5663,10 +5667,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>511876</v>
+        <v>511842</v>
       </c>
       <c r="R47" t="n">
-        <v>6984163</v>
+        <v>6984141</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5725,10 +5729,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118393885</v>
+        <v>118393897</v>
       </c>
       <c r="B48" t="n">
-        <v>97846</v>
+        <v>82263</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5737,42 +5741,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>511892</v>
+        <v>511911</v>
       </c>
       <c r="R48" t="n">
-        <v>6984185</v>
+        <v>6984171</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5831,10 +5831,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118393746</v>
+        <v>118393821</v>
       </c>
       <c r="B49" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5843,25 +5843,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5871,10 +5871,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>511842</v>
+        <v>511876</v>
       </c>
       <c r="R49" t="n">
-        <v>6984141</v>
+        <v>6984163</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 22554-2024 artfynd.xlsx
+++ b/artfynd/A 22554-2024 artfynd.xlsx
@@ -3331,10 +3331,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118393935</v>
+        <v>118394901</v>
       </c>
       <c r="B26" t="n">
-        <v>82263</v>
+        <v>57290</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3347,37 +3347,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511922</v>
+        <v>511694</v>
       </c>
       <c r="R26" t="n">
-        <v>6984163</v>
+        <v>6984128</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3404,9 +3409,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3433,10 +3448,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118394248</v>
+        <v>118393935</v>
       </c>
       <c r="B27" t="n">
-        <v>90504</v>
+        <v>82263</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3449,21 +3464,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3473,10 +3488,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511950</v>
+        <v>511922</v>
       </c>
       <c r="R27" t="n">
-        <v>6984198</v>
+        <v>6984163</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3535,7 +3550,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118394327</v>
+        <v>118394248</v>
       </c>
       <c r="B28" t="n">
         <v>90504</v>
@@ -3575,13 +3590,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>511917</v>
+        <v>511950</v>
       </c>
       <c r="R28" t="n">
-        <v>6984200</v>
+        <v>6984198</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3608,19 +3623,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3647,10 +3652,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118393472</v>
+        <v>118394327</v>
       </c>
       <c r="B29" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3659,45 +3664,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511752</v>
+        <v>511917</v>
       </c>
       <c r="R29" t="n">
-        <v>6984084</v>
+        <v>6984200</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3724,9 +3725,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3753,10 +3764,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118395030</v>
+        <v>118393626</v>
       </c>
       <c r="B30" t="n">
-        <v>97846</v>
+        <v>78484</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3765,38 +3776,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511734</v>
+        <v>511824</v>
       </c>
       <c r="R30" t="n">
-        <v>6984117</v>
+        <v>6984090</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3855,10 +3871,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118394298</v>
+        <v>118394207</v>
       </c>
       <c r="B31" t="n">
-        <v>97846</v>
+        <v>74596</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3867,45 +3883,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>511911</v>
+        <v>511968</v>
       </c>
       <c r="R31" t="n">
-        <v>6984196</v>
+        <v>6984167</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3932,9 +3944,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3961,10 +3983,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118394901</v>
+        <v>118393472</v>
       </c>
       <c r="B32" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3973,31 +3995,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4006,13 +4027,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>511694</v>
+        <v>511752</v>
       </c>
       <c r="R32" t="n">
-        <v>6984128</v>
+        <v>6984084</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4039,19 +4060,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4078,10 +4089,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118393626</v>
+        <v>118395030</v>
       </c>
       <c r="B33" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4090,43 +4101,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>511824</v>
+        <v>511734</v>
       </c>
       <c r="R33" t="n">
-        <v>6984090</v>
+        <v>6984117</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4185,10 +4191,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118394207</v>
+        <v>118394298</v>
       </c>
       <c r="B34" t="n">
-        <v>74596</v>
+        <v>97846</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4197,41 +4203,45 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>511968</v>
+        <v>511911</v>
       </c>
       <c r="R34" t="n">
-        <v>6984167</v>
+        <v>6984196</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4258,19 +4268,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5191,10 +5191,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118394417</v>
+        <v>118394030</v>
       </c>
       <c r="B43" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5203,50 +5203,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>511856</v>
+        <v>512003</v>
       </c>
       <c r="R43" t="n">
-        <v>6984192</v>
+        <v>6984152</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5273,19 +5264,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5312,10 +5293,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118394030</v>
+        <v>118394417</v>
       </c>
       <c r="B44" t="n">
-        <v>90504</v>
+        <v>97846</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5324,41 +5305,50 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>512003</v>
+        <v>511856</v>
       </c>
       <c r="R44" t="n">
-        <v>6984152</v>
+        <v>6984192</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5385,9 +5375,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 22554-2024 artfynd.xlsx
+++ b/artfynd/A 22554-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118394182</v>
+        <v>118394590</v>
       </c>
       <c r="B2" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,45 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>14</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512007</v>
+        <v>511742</v>
       </c>
       <c r="R2" t="n">
-        <v>6984193</v>
+        <v>6984146</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,9 +753,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118394590</v>
+        <v>118393626</v>
       </c>
       <c r="B3" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,27 +808,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -826,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511742</v>
+        <v>511824</v>
       </c>
       <c r="R3" t="n">
-        <v>6984146</v>
+        <v>6984090</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,19 +870,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118393904</v>
+        <v>118394182</v>
       </c>
       <c r="B4" t="n">
         <v>97846</v>
@@ -933,7 +934,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -942,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511906</v>
+        <v>512007</v>
       </c>
       <c r="R4" t="n">
-        <v>6984171</v>
+        <v>6984193</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1125,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118393891</v>
+        <v>118393150</v>
       </c>
       <c r="B6" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,42 +1142,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511918</v>
+        <v>511703</v>
       </c>
       <c r="R6" t="n">
-        <v>6984109</v>
+        <v>6984085</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,19 +1199,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118394581</v>
+        <v>118393974</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,45 +1240,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>9</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511742</v>
+        <v>511892</v>
       </c>
       <c r="R7" t="n">
-        <v>6984149</v>
+        <v>6984124</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,9 +1306,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,7 +1345,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118393135</v>
+        <v>118394581</v>
       </c>
       <c r="B8" t="n">
         <v>97846</v>
@@ -1383,7 +1380,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1392,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511692</v>
+        <v>511742</v>
       </c>
       <c r="R8" t="n">
-        <v>6984065</v>
+        <v>6984149</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118394125</v>
+        <v>118394680</v>
       </c>
       <c r="B9" t="n">
-        <v>90947</v>
+        <v>97846</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,40 +1467,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Småmyrarna, Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512008</v>
+        <v>511723</v>
       </c>
       <c r="R9" t="n">
-        <v>6984144</v>
+        <v>6984123</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1551,7 +1554,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1570,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118393108</v>
+        <v>118394417</v>
       </c>
       <c r="B10" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1582,46 +1584,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511701</v>
+        <v>511856</v>
       </c>
       <c r="R10" t="n">
-        <v>6984061</v>
+        <v>6984192</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1648,9 +1654,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1783,10 +1799,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118394693</v>
+        <v>118393935</v>
       </c>
       <c r="B12" t="n">
-        <v>57290</v>
+        <v>82263</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1799,39 +1815,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511716</v>
+        <v>511922</v>
       </c>
       <c r="R12" t="n">
-        <v>6984145</v>
+        <v>6984163</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1890,7 +1901,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118393044</v>
+        <v>118393897</v>
       </c>
       <c r="B13" t="n">
         <v>82263</v>
@@ -1926,14 +1937,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511724</v>
+        <v>511911</v>
       </c>
       <c r="R13" t="n">
-        <v>6984047</v>
+        <v>6984171</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1992,10 +2003,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118393346</v>
+        <v>118394125</v>
       </c>
       <c r="B14" t="n">
-        <v>90858</v>
+        <v>90947</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2008,37 +2019,40 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1506</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511769</v>
+        <v>512008</v>
       </c>
       <c r="R14" t="n">
-        <v>6984090</v>
+        <v>6984144</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2080,17 +2094,13 @@
           <t>13:14</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Grov granlåga</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2109,10 +2119,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118393802</v>
+        <v>118393392</v>
       </c>
       <c r="B15" t="n">
-        <v>97846</v>
+        <v>90469</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2121,45 +2131,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511869</v>
+        <v>511727</v>
       </c>
       <c r="R15" t="n">
-        <v>6984157</v>
+        <v>6984085</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2186,9 +2192,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2215,10 +2231,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118393818</v>
+        <v>118394396</v>
       </c>
       <c r="B16" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2227,35 +2243,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2264,13 +2276,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511903</v>
+        <v>511862</v>
       </c>
       <c r="R16" t="n">
-        <v>6984128</v>
+        <v>6984169</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2297,19 +2309,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2336,10 +2338,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118394668</v>
+        <v>118394566</v>
       </c>
       <c r="B17" t="n">
-        <v>95394</v>
+        <v>57290</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2352,37 +2354,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511726</v>
+        <v>511761</v>
       </c>
       <c r="R17" t="n">
-        <v>6984123</v>
+        <v>6984157</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2409,19 +2416,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2448,10 +2445,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118394680</v>
+        <v>118394901</v>
       </c>
       <c r="B18" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2460,35 +2457,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2497,10 +2490,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511723</v>
+        <v>511694</v>
       </c>
       <c r="R18" t="n">
-        <v>6984123</v>
+        <v>6984128</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2569,7 +2562,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118394560</v>
+        <v>118395009</v>
       </c>
       <c r="B19" t="n">
         <v>97846</v>
@@ -2602,24 +2595,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511770</v>
+        <v>511731</v>
       </c>
       <c r="R19" t="n">
-        <v>6984157</v>
+        <v>6984133</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2646,9 +2635,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2675,10 +2674,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118394566</v>
+        <v>118393904</v>
       </c>
       <c r="B20" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2687,43 +2686,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511761</v>
+        <v>511906</v>
       </c>
       <c r="R20" t="n">
-        <v>6984157</v>
+        <v>6984171</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2782,10 +2780,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118392836</v>
+        <v>118393891</v>
       </c>
       <c r="B21" t="n">
-        <v>90504</v>
+        <v>57290</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2798,37 +2796,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511716</v>
+        <v>511918</v>
       </c>
       <c r="R21" t="n">
-        <v>6984042</v>
+        <v>6984109</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2855,9 +2858,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2884,10 +2897,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118394550</v>
+        <v>118393726</v>
       </c>
       <c r="B22" t="n">
-        <v>90522</v>
+        <v>97846</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2896,41 +2909,50 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511801</v>
+        <v>511843</v>
       </c>
       <c r="R22" t="n">
-        <v>6984151</v>
+        <v>6984124</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2957,9 +2979,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3098,10 +3130,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118393861</v>
+        <v>118394550</v>
       </c>
       <c r="B24" t="n">
-        <v>97846</v>
+        <v>90522</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3110,50 +3142,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>511914</v>
+        <v>511801</v>
       </c>
       <c r="R24" t="n">
-        <v>6984121</v>
+        <v>6984151</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3180,19 +3203,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3219,10 +3232,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118395009</v>
+        <v>118394327</v>
       </c>
       <c r="B25" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3231,38 +3244,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511731</v>
+        <v>511917</v>
       </c>
       <c r="R25" t="n">
-        <v>6984133</v>
+        <v>6984200</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3331,7 +3344,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118394901</v>
+        <v>118394693</v>
       </c>
       <c r="B26" t="n">
         <v>57290</v>
@@ -3376,13 +3389,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511694</v>
+        <v>511716</v>
       </c>
       <c r="R26" t="n">
-        <v>6984128</v>
+        <v>6984145</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3409,19 +3422,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3448,10 +3451,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118393935</v>
+        <v>118394668</v>
       </c>
       <c r="B27" t="n">
-        <v>82263</v>
+        <v>95394</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3464,37 +3467,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511922</v>
+        <v>511726</v>
       </c>
       <c r="R27" t="n">
-        <v>6984163</v>
+        <v>6984123</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3521,9 +3524,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3550,7 +3563,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118394248</v>
+        <v>118394030</v>
       </c>
       <c r="B28" t="n">
         <v>90504</v>
@@ -3590,10 +3603,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>511950</v>
+        <v>512003</v>
       </c>
       <c r="R28" t="n">
-        <v>6984198</v>
+        <v>6984152</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3652,10 +3665,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118394327</v>
+        <v>118393108</v>
       </c>
       <c r="B29" t="n">
-        <v>90504</v>
+        <v>57290</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3668,37 +3681,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511917</v>
+        <v>511701</v>
       </c>
       <c r="R29" t="n">
-        <v>6984200</v>
+        <v>6984061</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3725,19 +3743,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3764,10 +3772,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118393626</v>
+        <v>118393902</v>
       </c>
       <c r="B30" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3776,46 +3784,50 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511824</v>
+        <v>511908</v>
       </c>
       <c r="R30" t="n">
-        <v>6984090</v>
+        <v>6984095</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3842,9 +3854,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3871,10 +3893,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118394207</v>
+        <v>118393135</v>
       </c>
       <c r="B31" t="n">
-        <v>74596</v>
+        <v>97846</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3883,41 +3905,45 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>511968</v>
+        <v>511692</v>
       </c>
       <c r="R31" t="n">
-        <v>6984167</v>
+        <v>6984065</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3944,19 +3970,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3983,7 +3999,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118393472</v>
+        <v>118394560</v>
       </c>
       <c r="B32" t="n">
         <v>97846</v>
@@ -4018,7 +4034,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4027,10 +4043,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>511752</v>
+        <v>511770</v>
       </c>
       <c r="R32" t="n">
-        <v>6984084</v>
+        <v>6984157</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4089,7 +4105,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118395030</v>
+        <v>118393861</v>
       </c>
       <c r="B33" t="n">
         <v>97846</v>
@@ -4122,20 +4138,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>511734</v>
+        <v>511914</v>
       </c>
       <c r="R33" t="n">
-        <v>6984117</v>
+        <v>6984121</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4162,9 +4187,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4191,10 +4226,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118394298</v>
+        <v>118392836</v>
       </c>
       <c r="B34" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4203,42 +4238,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>511911</v>
+        <v>511716</v>
       </c>
       <c r="R34" t="n">
-        <v>6984196</v>
+        <v>6984042</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4414,10 +4445,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118393392</v>
+        <v>118394426</v>
       </c>
       <c r="B36" t="n">
-        <v>90469</v>
+        <v>79565</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4426,41 +4457,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>511727</v>
+        <v>511815</v>
       </c>
       <c r="R36" t="n">
-        <v>6984085</v>
+        <v>6984155</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4487,19 +4518,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4526,10 +4547,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118393974</v>
+        <v>118393868</v>
       </c>
       <c r="B37" t="n">
-        <v>79565</v>
+        <v>74588</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4542,42 +4563,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>511892</v>
+        <v>511869</v>
       </c>
       <c r="R37" t="n">
-        <v>6984124</v>
+        <v>6984163</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4604,19 +4620,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4643,10 +4649,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118393150</v>
+        <v>118393346</v>
       </c>
       <c r="B38" t="n">
-        <v>78484</v>
+        <v>90858</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4655,25 +4661,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4683,13 +4689,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>511703</v>
+        <v>511769</v>
       </c>
       <c r="R38" t="n">
-        <v>6984085</v>
+        <v>6984090</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4716,9 +4722,24 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Grov granlåga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4745,7 +4766,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118393902</v>
+        <v>118395030</v>
       </c>
       <c r="B39" t="n">
         <v>97846</v>
@@ -4778,29 +4799,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>511908</v>
+        <v>511734</v>
       </c>
       <c r="R39" t="n">
-        <v>6984095</v>
+        <v>6984117</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4827,19 +4839,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4866,10 +4868,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118393726</v>
+        <v>118394248</v>
       </c>
       <c r="B40" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4878,50 +4880,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>511843</v>
+        <v>511950</v>
       </c>
       <c r="R40" t="n">
-        <v>6984124</v>
+        <v>6984198</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4948,19 +4941,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4987,10 +4970,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118393868</v>
+        <v>118393044</v>
       </c>
       <c r="B41" t="n">
-        <v>74588</v>
+        <v>82263</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5003,34 +4986,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>511869</v>
+        <v>511724</v>
       </c>
       <c r="R41" t="n">
-        <v>6984163</v>
+        <v>6984047</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5089,7 +5072,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118394426</v>
+        <v>118393821</v>
       </c>
       <c r="B42" t="n">
         <v>79565</v>
@@ -5129,10 +5112,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>511815</v>
+        <v>511876</v>
       </c>
       <c r="R42" t="n">
-        <v>6984155</v>
+        <v>6984163</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5191,10 +5174,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118394030</v>
+        <v>118393472</v>
       </c>
       <c r="B43" t="n">
-        <v>90504</v>
+        <v>97846</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5203,38 +5186,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>512003</v>
+        <v>511752</v>
       </c>
       <c r="R43" t="n">
-        <v>6984152</v>
+        <v>6984084</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5293,7 +5280,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118394417</v>
+        <v>118393802</v>
       </c>
       <c r="B44" t="n">
         <v>97846</v>
@@ -5328,12 +5315,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5342,13 +5324,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>511856</v>
+        <v>511869</v>
       </c>
       <c r="R44" t="n">
-        <v>6984192</v>
+        <v>6984157</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5375,19 +5357,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5414,10 +5386,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118394396</v>
+        <v>118394298</v>
       </c>
       <c r="B45" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5426,31 +5398,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5459,10 +5430,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>511862</v>
+        <v>511911</v>
       </c>
       <c r="R45" t="n">
-        <v>6984169</v>
+        <v>6984196</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5729,10 +5700,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118393897</v>
+        <v>118393818</v>
       </c>
       <c r="B48" t="n">
-        <v>82263</v>
+        <v>97846</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5741,41 +5712,50 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>511911</v>
+        <v>511903</v>
       </c>
       <c r="R48" t="n">
-        <v>6984171</v>
+        <v>6984128</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5802,9 +5782,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5831,10 +5821,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118393821</v>
+        <v>118394207</v>
       </c>
       <c r="B49" t="n">
-        <v>79565</v>
+        <v>74596</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5847,21 +5837,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5871,13 +5861,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>511876</v>
+        <v>511968</v>
       </c>
       <c r="R49" t="n">
-        <v>6984163</v>
+        <v>6984167</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5904,9 +5894,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 22554-2024 artfynd.xlsx
+++ b/artfynd/A 22554-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118394590</v>
+        <v>118393626</v>
       </c>
       <c r="B2" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511742</v>
+        <v>511824</v>
       </c>
       <c r="R2" t="n">
-        <v>6984146</v>
+        <v>6984090</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,19 +753,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118393626</v>
+        <v>118394590</v>
       </c>
       <c r="B3" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,27 +798,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511824</v>
+        <v>511742</v>
       </c>
       <c r="R3" t="n">
-        <v>6984090</v>
+        <v>6984146</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,9 +860,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -2119,10 +2119,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118393392</v>
+        <v>118394396</v>
       </c>
       <c r="B15" t="n">
-        <v>90469</v>
+        <v>57290</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2131,41 +2131,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511727</v>
+        <v>511862</v>
       </c>
       <c r="R15" t="n">
-        <v>6984085</v>
+        <v>6984169</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2192,19 +2197,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,7 +2226,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118394396</v>
+        <v>118394566</v>
       </c>
       <c r="B16" t="n">
         <v>57290</v>
@@ -2272,14 +2267,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511862</v>
+        <v>511761</v>
       </c>
       <c r="R16" t="n">
-        <v>6984169</v>
+        <v>6984157</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2338,7 +2333,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118394566</v>
+        <v>118394901</v>
       </c>
       <c r="B17" t="n">
         <v>57290</v>
@@ -2383,13 +2378,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511761</v>
+        <v>511694</v>
       </c>
       <c r="R17" t="n">
-        <v>6984157</v>
+        <v>6984128</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2416,9 +2411,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2445,10 +2450,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118394901</v>
+        <v>118395009</v>
       </c>
       <c r="B18" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2457,43 +2462,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511694</v>
+        <v>511731</v>
       </c>
       <c r="R18" t="n">
-        <v>6984128</v>
+        <v>6984133</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2562,7 +2562,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118395009</v>
+        <v>118393904</v>
       </c>
       <c r="B19" t="n">
         <v>97846</v>
@@ -2595,20 +2595,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511731</v>
+        <v>511906</v>
       </c>
       <c r="R19" t="n">
-        <v>6984133</v>
+        <v>6984171</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2635,19 +2639,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2674,10 +2668,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118393904</v>
+        <v>118393392</v>
       </c>
       <c r="B20" t="n">
-        <v>97846</v>
+        <v>90469</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2686,45 +2680,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511906</v>
+        <v>511727</v>
       </c>
       <c r="R20" t="n">
-        <v>6984171</v>
+        <v>6984085</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2751,9 +2741,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3772,10 +3772,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118393902</v>
+        <v>118393469</v>
       </c>
       <c r="B30" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3784,47 +3784,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511908</v>
+        <v>511791</v>
       </c>
       <c r="R30" t="n">
-        <v>6984095</v>
+        <v>6984074</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3893,7 +3889,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118393135</v>
+        <v>118393902</v>
       </c>
       <c r="B31" t="n">
         <v>97846</v>
@@ -3928,22 +3924,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>511692</v>
+        <v>511908</v>
       </c>
       <c r="R31" t="n">
-        <v>6984065</v>
+        <v>6984095</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3970,9 +3971,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3999,7 +4010,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118394560</v>
+        <v>118393135</v>
       </c>
       <c r="B32" t="n">
         <v>97846</v>
@@ -4034,7 +4045,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4043,10 +4054,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>511770</v>
+        <v>511692</v>
       </c>
       <c r="R32" t="n">
-        <v>6984157</v>
+        <v>6984065</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4105,7 +4116,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118393861</v>
+        <v>118394560</v>
       </c>
       <c r="B33" t="n">
         <v>97846</v>
@@ -4140,27 +4151,22 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>511914</v>
+        <v>511770</v>
       </c>
       <c r="R33" t="n">
-        <v>6984121</v>
+        <v>6984157</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4187,19 +4193,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4226,10 +4222,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118392836</v>
+        <v>118393861</v>
       </c>
       <c r="B34" t="n">
-        <v>90504</v>
+        <v>97846</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4238,41 +4234,50 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>511716</v>
+        <v>511914</v>
       </c>
       <c r="R34" t="n">
-        <v>6984042</v>
+        <v>6984121</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4299,9 +4304,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4328,10 +4343,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118393469</v>
+        <v>118392836</v>
       </c>
       <c r="B35" t="n">
-        <v>57290</v>
+        <v>90504</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4344,42 +4359,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>511791</v>
+        <v>511716</v>
       </c>
       <c r="R35" t="n">
-        <v>6984074</v>
+        <v>6984042</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4406,19 +4416,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4649,10 +4649,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118393346</v>
+        <v>118395030</v>
       </c>
       <c r="B38" t="n">
-        <v>90858</v>
+        <v>97846</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4665,21 +4665,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1506</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4689,13 +4689,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>511769</v>
+        <v>511734</v>
       </c>
       <c r="R38" t="n">
-        <v>6984090</v>
+        <v>6984117</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4722,24 +4722,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Grov granlåga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4766,10 +4751,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118395030</v>
+        <v>118393346</v>
       </c>
       <c r="B39" t="n">
-        <v>97846</v>
+        <v>90858</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4782,21 +4767,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>1506</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4806,13 +4791,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>511734</v>
+        <v>511769</v>
       </c>
       <c r="R39" t="n">
-        <v>6984117</v>
+        <v>6984090</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4839,9 +4824,24 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Grov granlåga</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 22554-2024 artfynd.xlsx
+++ b/artfynd/A 22554-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118393626</v>
+        <v>118393346</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
+        <v>90858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511824</v>
+        <v>511769</v>
       </c>
       <c r="R2" t="n">
         <v>6984090</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,9 +748,24 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Grov granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118394590</v>
+        <v>118393100</v>
       </c>
       <c r="B3" t="n">
-        <v>57290</v>
+        <v>79593</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,43 +804,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511742</v>
+        <v>511722</v>
       </c>
       <c r="R3" t="n">
-        <v>6984146</v>
+        <v>6984095</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118394182</v>
+        <v>118394668</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>95394</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,45 +916,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512007</v>
+        <v>511726</v>
       </c>
       <c r="R4" t="n">
-        <v>6984193</v>
+        <v>6984123</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,9 +977,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118393781</v>
+        <v>118395009</v>
       </c>
       <c r="B5" t="n">
         <v>97846</v>
@@ -1038,26 +1049,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511873</v>
+        <v>511731</v>
       </c>
       <c r="R5" t="n">
-        <v>6984099</v>
+        <v>6984133</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1126,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118393150</v>
+        <v>118393861</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,41 +1140,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511703</v>
+        <v>511914</v>
       </c>
       <c r="R6" t="n">
-        <v>6984085</v>
+        <v>6984121</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1199,9 +1210,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118393974</v>
+        <v>118394125</v>
       </c>
       <c r="B7" t="n">
-        <v>79565</v>
+        <v>90947</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,46 +1261,44 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Småmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511892</v>
+        <v>512008</v>
       </c>
       <c r="R7" t="n">
-        <v>6984124</v>
+        <v>6984144</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1327,6 +1346,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1345,7 +1365,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118394581</v>
+        <v>118393885</v>
       </c>
       <c r="B8" t="n">
         <v>97846</v>
@@ -1380,19 +1400,19 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511742</v>
+        <v>511892</v>
       </c>
       <c r="R8" t="n">
-        <v>6984149</v>
+        <v>6984185</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,10 +1471,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118394680</v>
+        <v>118393108</v>
       </c>
       <c r="B9" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1463,35 +1483,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1500,13 +1516,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511723</v>
+        <v>511701</v>
       </c>
       <c r="R9" t="n">
-        <v>6984123</v>
+        <v>6984061</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1533,19 +1549,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1572,10 +1578,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118394417</v>
+        <v>118394550</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
+        <v>90522</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,50 +1590,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511856</v>
+        <v>511801</v>
       </c>
       <c r="R10" t="n">
-        <v>6984192</v>
+        <v>6984151</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1654,19 +1651,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,7 +1680,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118393753</v>
+        <v>118394298</v>
       </c>
       <c r="B11" t="n">
         <v>97846</v>
@@ -1728,7 +1715,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1737,10 +1724,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511841</v>
+        <v>511911</v>
       </c>
       <c r="R11" t="n">
-        <v>6984146</v>
+        <v>6984196</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1799,10 +1786,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118393935</v>
+        <v>118393746</v>
       </c>
       <c r="B12" t="n">
-        <v>82263</v>
+        <v>97846</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,25 +1798,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1839,10 +1826,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511922</v>
+        <v>511842</v>
       </c>
       <c r="R12" t="n">
-        <v>6984163</v>
+        <v>6984141</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,10 +1888,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118393897</v>
+        <v>118392836</v>
       </c>
       <c r="B13" t="n">
-        <v>82263</v>
+        <v>90504</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1917,34 +1904,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511911</v>
+        <v>511716</v>
       </c>
       <c r="R13" t="n">
-        <v>6984171</v>
+        <v>6984042</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2003,10 +1990,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118394125</v>
+        <v>118394693</v>
       </c>
       <c r="B14" t="n">
-        <v>90947</v>
+        <v>57290</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2015,44 +2002,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Småmyrarna, Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>512008</v>
+        <v>511716</v>
       </c>
       <c r="R14" t="n">
-        <v>6984144</v>
+        <v>6984145</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2079,28 +2068,17 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2119,10 +2097,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118394396</v>
+        <v>118393802</v>
       </c>
       <c r="B15" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2131,31 +2109,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2164,10 +2141,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511862</v>
+        <v>511869</v>
       </c>
       <c r="R15" t="n">
-        <v>6984169</v>
+        <v>6984157</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2226,10 +2203,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118394566</v>
+        <v>118395030</v>
       </c>
       <c r="B16" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2238,43 +2215,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511761</v>
+        <v>511734</v>
       </c>
       <c r="R16" t="n">
-        <v>6984157</v>
+        <v>6984117</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2333,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118394901</v>
+        <v>118393868</v>
       </c>
       <c r="B17" t="n">
-        <v>57290</v>
+        <v>74588</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2349,42 +2321,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511694</v>
+        <v>511869</v>
       </c>
       <c r="R17" t="n">
-        <v>6984128</v>
+        <v>6984163</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2411,19 +2378,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2450,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118395009</v>
+        <v>118393935</v>
       </c>
       <c r="B18" t="n">
-        <v>97846</v>
+        <v>82263</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2462,41 +2419,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511731</v>
+        <v>511922</v>
       </c>
       <c r="R18" t="n">
-        <v>6984133</v>
+        <v>6984163</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2523,19 +2480,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2562,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118393904</v>
+        <v>118394248</v>
       </c>
       <c r="B19" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2574,42 +2521,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511906</v>
+        <v>511950</v>
       </c>
       <c r="R19" t="n">
-        <v>6984171</v>
+        <v>6984198</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2668,10 +2611,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118393392</v>
+        <v>118394030</v>
       </c>
       <c r="B20" t="n">
-        <v>90469</v>
+        <v>90504</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2680,41 +2623,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511727</v>
+        <v>512003</v>
       </c>
       <c r="R20" t="n">
-        <v>6984085</v>
+        <v>6984152</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2741,19 +2684,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2780,10 +2713,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118393891</v>
+        <v>118393904</v>
       </c>
       <c r="B21" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2792,31 +2725,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2825,13 +2757,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511918</v>
+        <v>511906</v>
       </c>
       <c r="R21" t="n">
-        <v>6984109</v>
+        <v>6984171</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2858,19 +2790,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2897,10 +2819,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118393726</v>
+        <v>118394566</v>
       </c>
       <c r="B22" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2909,50 +2831,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511843</v>
+        <v>511761</v>
       </c>
       <c r="R22" t="n">
-        <v>6984124</v>
+        <v>6984157</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2979,19 +2897,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3018,10 +2926,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118393100</v>
+        <v>118393469</v>
       </c>
       <c r="B23" t="n">
-        <v>79593</v>
+        <v>57290</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3030,38 +2938,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>511722</v>
+        <v>511791</v>
       </c>
       <c r="R23" t="n">
-        <v>6984095</v>
+        <v>6984074</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3130,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118394550</v>
+        <v>118394207</v>
       </c>
       <c r="B24" t="n">
-        <v>90522</v>
+        <v>74596</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3146,21 +3059,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3170,13 +3083,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>511801</v>
+        <v>511968</v>
       </c>
       <c r="R24" t="n">
-        <v>6984151</v>
+        <v>6984167</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3203,9 +3116,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3232,10 +3155,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118394327</v>
+        <v>118394426</v>
       </c>
       <c r="B25" t="n">
-        <v>90504</v>
+        <v>79565</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3248,21 +3171,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3272,13 +3195,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511917</v>
+        <v>511815</v>
       </c>
       <c r="R25" t="n">
-        <v>6984200</v>
+        <v>6984155</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3305,19 +3228,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3344,7 +3257,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118394693</v>
+        <v>118394901</v>
       </c>
       <c r="B26" t="n">
         <v>57290</v>
@@ -3389,13 +3302,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511716</v>
+        <v>511694</v>
       </c>
       <c r="R26" t="n">
-        <v>6984145</v>
+        <v>6984128</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3422,9 +3335,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3451,10 +3374,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118394668</v>
+        <v>118393891</v>
       </c>
       <c r="B27" t="n">
-        <v>95394</v>
+        <v>57290</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3467,34 +3390,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511726</v>
+        <v>511918</v>
       </c>
       <c r="R27" t="n">
-        <v>6984123</v>
+        <v>6984109</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3563,10 +3491,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118394030</v>
+        <v>118393150</v>
       </c>
       <c r="B28" t="n">
-        <v>90504</v>
+        <v>78484</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3579,34 +3507,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>512003</v>
+        <v>511703</v>
       </c>
       <c r="R28" t="n">
-        <v>6984152</v>
+        <v>6984085</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3665,10 +3593,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118393108</v>
+        <v>118394680</v>
       </c>
       <c r="B29" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3677,31 +3605,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3710,13 +3642,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511701</v>
+        <v>511723</v>
       </c>
       <c r="R29" t="n">
-        <v>6984061</v>
+        <v>6984123</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3743,9 +3675,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3772,7 +3714,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118393469</v>
+        <v>118394590</v>
       </c>
       <c r="B30" t="n">
         <v>57290</v>
@@ -3817,10 +3759,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511791</v>
+        <v>511742</v>
       </c>
       <c r="R30" t="n">
-        <v>6984074</v>
+        <v>6984146</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3889,10 +3831,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118393902</v>
+        <v>118393974</v>
       </c>
       <c r="B31" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3901,35 +3843,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3938,10 +3876,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>511908</v>
+        <v>511892</v>
       </c>
       <c r="R31" t="n">
-        <v>6984095</v>
+        <v>6984124</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4010,7 +3948,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118393135</v>
+        <v>118394182</v>
       </c>
       <c r="B32" t="n">
         <v>97846</v>
@@ -4045,19 +3983,19 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>511692</v>
+        <v>512007</v>
       </c>
       <c r="R32" t="n">
-        <v>6984065</v>
+        <v>6984193</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4116,7 +4054,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118394560</v>
+        <v>118393753</v>
       </c>
       <c r="B33" t="n">
         <v>97846</v>
@@ -4151,19 +4089,19 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>511770</v>
+        <v>511841</v>
       </c>
       <c r="R33" t="n">
-        <v>6984157</v>
+        <v>6984146</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4222,7 +4160,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118393861</v>
+        <v>118394560</v>
       </c>
       <c r="B34" t="n">
         <v>97846</v>
@@ -4257,27 +4195,22 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>511914</v>
+        <v>511770</v>
       </c>
       <c r="R34" t="n">
-        <v>6984121</v>
+        <v>6984157</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4304,19 +4237,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4343,10 +4266,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118392836</v>
+        <v>118394581</v>
       </c>
       <c r="B35" t="n">
-        <v>90504</v>
+        <v>97846</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4355,38 +4278,42 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>511716</v>
+        <v>511742</v>
       </c>
       <c r="R35" t="n">
-        <v>6984042</v>
+        <v>6984149</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4445,10 +4372,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118394426</v>
+        <v>118393902</v>
       </c>
       <c r="B36" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4457,41 +4384,50 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>511815</v>
+        <v>511908</v>
       </c>
       <c r="R36" t="n">
-        <v>6984155</v>
+        <v>6984095</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4518,9 +4454,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4547,10 +4493,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118393868</v>
+        <v>118393135</v>
       </c>
       <c r="B37" t="n">
-        <v>74588</v>
+        <v>97846</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4559,38 +4505,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>511869</v>
+        <v>511692</v>
       </c>
       <c r="R37" t="n">
-        <v>6984163</v>
+        <v>6984065</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4649,7 +4599,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118395030</v>
+        <v>118394417</v>
       </c>
       <c r="B38" t="n">
         <v>97846</v>
@@ -4682,20 +4632,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>511734</v>
+        <v>511856</v>
       </c>
       <c r="R38" t="n">
-        <v>6984117</v>
+        <v>6984192</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4722,9 +4681,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4751,10 +4720,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118393346</v>
+        <v>118393044</v>
       </c>
       <c r="B39" t="n">
-        <v>90858</v>
+        <v>82263</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4763,25 +4732,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1506</v>
+        <v>1312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4791,13 +4760,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>511769</v>
+        <v>511724</v>
       </c>
       <c r="R39" t="n">
-        <v>6984090</v>
+        <v>6984047</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4824,24 +4793,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Grov granlåga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4868,10 +4822,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118394248</v>
+        <v>118393897</v>
       </c>
       <c r="B40" t="n">
-        <v>90504</v>
+        <v>82263</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4884,21 +4838,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4908,10 +4862,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>511950</v>
+        <v>511911</v>
       </c>
       <c r="R40" t="n">
-        <v>6984198</v>
+        <v>6984171</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4970,10 +4924,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118393044</v>
+        <v>118393392</v>
       </c>
       <c r="B41" t="n">
-        <v>82263</v>
+        <v>90469</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4982,25 +4936,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5010,13 +4964,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>511724</v>
+        <v>511727</v>
       </c>
       <c r="R41" t="n">
-        <v>6984047</v>
+        <v>6984085</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5043,9 +4997,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5072,10 +5036,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118393821</v>
+        <v>118393626</v>
       </c>
       <c r="B42" t="n">
-        <v>79565</v>
+        <v>78484</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5088,34 +5052,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>511876</v>
+        <v>511824</v>
       </c>
       <c r="R42" t="n">
-        <v>6984163</v>
+        <v>6984090</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5174,10 +5143,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118393472</v>
+        <v>118394327</v>
       </c>
       <c r="B43" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5186,45 +5155,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>511752</v>
+        <v>511917</v>
       </c>
       <c r="R43" t="n">
-        <v>6984084</v>
+        <v>6984200</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5251,9 +5216,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5280,10 +5255,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118393802</v>
+        <v>118394396</v>
       </c>
       <c r="B44" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5292,30 +5267,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>11</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5324,10 +5300,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>511869</v>
+        <v>511862</v>
       </c>
       <c r="R44" t="n">
-        <v>6984157</v>
+        <v>6984169</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5386,7 +5362,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118394298</v>
+        <v>118393726</v>
       </c>
       <c r="B45" t="n">
         <v>97846</v>
@@ -5421,7 +5397,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5430,13 +5411,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>511911</v>
+        <v>511843</v>
       </c>
       <c r="R45" t="n">
-        <v>6984196</v>
+        <v>6984124</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5463,9 +5444,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5492,10 +5483,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118393885</v>
+        <v>118393821</v>
       </c>
       <c r="B46" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5504,42 +5495,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>511892</v>
+        <v>511876</v>
       </c>
       <c r="R46" t="n">
-        <v>6984185</v>
+        <v>6984163</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5598,7 +5585,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118393746</v>
+        <v>118393472</v>
       </c>
       <c r="B47" t="n">
         <v>97846</v>
@@ -5631,17 +5618,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>511842</v>
+        <v>511752</v>
       </c>
       <c r="R47" t="n">
-        <v>6984141</v>
+        <v>6984084</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5821,10 +5812,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118394207</v>
+        <v>118393781</v>
       </c>
       <c r="B49" t="n">
-        <v>74596</v>
+        <v>97846</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5833,38 +5824,47 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>511968</v>
+        <v>511873</v>
       </c>
       <c r="R49" t="n">
-        <v>6984167</v>
+        <v>6984099</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>

--- a/artfynd/A 22554-2024 artfynd.xlsx
+++ b/artfynd/A 22554-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118393346</v>
+        <v>118394590</v>
       </c>
       <c r="B2" t="n">
-        <v>90858</v>
+        <v>57290</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1506</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511769</v>
+        <v>511742</v>
       </c>
       <c r="R2" t="n">
-        <v>6984090</v>
+        <v>6984146</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -761,11 +766,6 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Grov granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118393100</v>
+        <v>118393726</v>
       </c>
       <c r="B3" t="n">
-        <v>79593</v>
+        <v>97853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,38 +804,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511722</v>
+        <v>511843</v>
       </c>
       <c r="R3" t="n">
-        <v>6984095</v>
+        <v>6984124</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -904,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118394668</v>
+        <v>118393746</v>
       </c>
       <c r="B4" t="n">
-        <v>95394</v>
+        <v>97853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,41 +925,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511726</v>
+        <v>511842</v>
       </c>
       <c r="R4" t="n">
-        <v>6984123</v>
+        <v>6984141</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,19 +986,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118395009</v>
+        <v>118394693</v>
       </c>
       <c r="B5" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,41 +1027,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511731</v>
+        <v>511716</v>
       </c>
       <c r="R5" t="n">
-        <v>6984133</v>
+        <v>6984145</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,19 +1093,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118393861</v>
+        <v>118395030</v>
       </c>
       <c r="B6" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,29 +1155,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511914</v>
+        <v>511734</v>
       </c>
       <c r="R6" t="n">
-        <v>6984121</v>
+        <v>6984117</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,19 +1195,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118394125</v>
+        <v>118394248</v>
       </c>
       <c r="B7" t="n">
-        <v>90947</v>
+        <v>90511</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,44 +1236,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Småmyrarna, Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512008</v>
+        <v>511950</v>
       </c>
       <c r="R7" t="n">
-        <v>6984144</v>
+        <v>6984198</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1325,28 +1297,17 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1365,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118393885</v>
+        <v>118393974</v>
       </c>
       <c r="B8" t="n">
-        <v>97846</v>
+        <v>79572</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,30 +1338,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1412,10 +1374,10 @@
         <v>511892</v>
       </c>
       <c r="R8" t="n">
-        <v>6984185</v>
+        <v>6984124</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1442,9 +1404,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118393108</v>
+        <v>118393821</v>
       </c>
       <c r="B9" t="n">
-        <v>57290</v>
+        <v>79572</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,39 +1459,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511701</v>
+        <v>511876</v>
       </c>
       <c r="R9" t="n">
-        <v>6984061</v>
+        <v>6984163</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1578,10 +1545,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118394550</v>
+        <v>118394566</v>
       </c>
       <c r="B10" t="n">
-        <v>90522</v>
+        <v>57290</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1594,34 +1561,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511801</v>
+        <v>511761</v>
       </c>
       <c r="R10" t="n">
-        <v>6984151</v>
+        <v>6984157</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,10 +1652,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118394298</v>
+        <v>118393469</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1692,45 +1664,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>11</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511911</v>
+        <v>511791</v>
       </c>
       <c r="R11" t="n">
-        <v>6984196</v>
+        <v>6984074</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1757,9 +1730,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1786,10 +1769,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118393746</v>
+        <v>118393135</v>
       </c>
       <c r="B12" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1819,17 +1802,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511842</v>
+        <v>511692</v>
       </c>
       <c r="R12" t="n">
-        <v>6984141</v>
+        <v>6984065</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1888,10 +1875,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118392836</v>
+        <v>118393861</v>
       </c>
       <c r="B13" t="n">
-        <v>90504</v>
+        <v>97853</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1900,41 +1887,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511716</v>
+        <v>511914</v>
       </c>
       <c r="R13" t="n">
-        <v>6984042</v>
+        <v>6984121</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1961,9 +1957,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1990,10 +1996,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118394693</v>
+        <v>118393781</v>
       </c>
       <c r="B14" t="n">
-        <v>57290</v>
+        <v>97853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2002,46 +2008,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511716</v>
+        <v>511873</v>
       </c>
       <c r="R14" t="n">
-        <v>6984145</v>
+        <v>6984099</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2068,9 +2078,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2097,10 +2117,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118393802</v>
+        <v>118394125</v>
       </c>
       <c r="B15" t="n">
-        <v>97846</v>
+        <v>90954</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2113,41 +2133,40 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Småmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511869</v>
+        <v>512008</v>
       </c>
       <c r="R15" t="n">
-        <v>6984157</v>
+        <v>6984144</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2174,17 +2193,28 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2203,10 +2233,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118395030</v>
+        <v>118394417</v>
       </c>
       <c r="B16" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2236,20 +2266,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511734</v>
+        <v>511856</v>
       </c>
       <c r="R16" t="n">
-        <v>6984117</v>
+        <v>6984192</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2276,9 +2315,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2305,10 +2354,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118393868</v>
+        <v>118393150</v>
       </c>
       <c r="B17" t="n">
-        <v>74588</v>
+        <v>78491</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2321,34 +2370,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511869</v>
+        <v>511703</v>
       </c>
       <c r="R17" t="n">
-        <v>6984163</v>
+        <v>6984085</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2407,10 +2456,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118393935</v>
+        <v>118394581</v>
       </c>
       <c r="B18" t="n">
-        <v>82263</v>
+        <v>97853</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2419,38 +2468,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511922</v>
+        <v>511742</v>
       </c>
       <c r="R18" t="n">
-        <v>6984163</v>
+        <v>6984149</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2509,10 +2562,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118394248</v>
+        <v>118393868</v>
       </c>
       <c r="B19" t="n">
-        <v>90504</v>
+        <v>74595</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2525,21 +2578,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2549,10 +2602,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511950</v>
+        <v>511869</v>
       </c>
       <c r="R19" t="n">
-        <v>6984198</v>
+        <v>6984163</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2611,10 +2664,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118394030</v>
+        <v>118392836</v>
       </c>
       <c r="B20" t="n">
-        <v>90504</v>
+        <v>90511</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2647,14 +2700,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>512003</v>
+        <v>511716</v>
       </c>
       <c r="R20" t="n">
-        <v>6984152</v>
+        <v>6984042</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2713,10 +2766,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118393904</v>
+        <v>118393472</v>
       </c>
       <c r="B21" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2748,19 +2801,19 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511906</v>
+        <v>511752</v>
       </c>
       <c r="R21" t="n">
-        <v>6984171</v>
+        <v>6984084</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2819,10 +2872,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118394566</v>
+        <v>118393885</v>
       </c>
       <c r="B22" t="n">
-        <v>57290</v>
+        <v>97853</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2831,43 +2884,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511761</v>
+        <v>511892</v>
       </c>
       <c r="R22" t="n">
-        <v>6984157</v>
+        <v>6984185</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2926,10 +2978,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118393469</v>
+        <v>118393044</v>
       </c>
       <c r="B23" t="n">
-        <v>57290</v>
+        <v>82270</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2942,42 +2994,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>511791</v>
+        <v>511724</v>
       </c>
       <c r="R23" t="n">
-        <v>6984074</v>
+        <v>6984047</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3004,19 +3051,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3043,10 +3080,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118394207</v>
+        <v>118393100</v>
       </c>
       <c r="B24" t="n">
-        <v>74596</v>
+        <v>79600</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3055,38 +3092,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>6461</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>511968</v>
+        <v>511722</v>
       </c>
       <c r="R24" t="n">
-        <v>6984167</v>
+        <v>6984095</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3155,10 +3192,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118394426</v>
+        <v>118393904</v>
       </c>
       <c r="B25" t="n">
-        <v>79565</v>
+        <v>97853</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3167,38 +3204,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511815</v>
+        <v>511906</v>
       </c>
       <c r="R25" t="n">
-        <v>6984155</v>
+        <v>6984171</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3257,10 +3298,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118394901</v>
+        <v>118394030</v>
       </c>
       <c r="B26" t="n">
-        <v>57290</v>
+        <v>90511</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3273,42 +3314,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511694</v>
+        <v>512003</v>
       </c>
       <c r="R26" t="n">
-        <v>6984128</v>
+        <v>6984152</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3335,19 +3371,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3374,10 +3400,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118393891</v>
+        <v>118393626</v>
       </c>
       <c r="B27" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3390,42 +3416,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511918</v>
+        <v>511824</v>
       </c>
       <c r="R27" t="n">
-        <v>6984109</v>
+        <v>6984090</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3452,19 +3478,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3491,10 +3507,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118393150</v>
+        <v>118394680</v>
       </c>
       <c r="B28" t="n">
-        <v>78484</v>
+        <v>97853</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3503,41 +3519,50 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>511703</v>
+        <v>511723</v>
       </c>
       <c r="R28" t="n">
-        <v>6984085</v>
+        <v>6984123</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3564,9 +3589,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3593,10 +3628,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118394680</v>
+        <v>118394327</v>
       </c>
       <c r="B29" t="n">
-        <v>97846</v>
+        <v>90511</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3605,47 +3640,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511723</v>
+        <v>511917</v>
       </c>
       <c r="R29" t="n">
-        <v>6984123</v>
+        <v>6984200</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3714,10 +3740,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118394590</v>
+        <v>118394550</v>
       </c>
       <c r="B30" t="n">
-        <v>57290</v>
+        <v>90529</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3730,42 +3756,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511742</v>
+        <v>511801</v>
       </c>
       <c r="R30" t="n">
-        <v>6984146</v>
+        <v>6984151</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3792,19 +3813,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3831,10 +3842,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118393974</v>
+        <v>118394426</v>
       </c>
       <c r="B31" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3865,24 +3876,19 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>511892</v>
+        <v>511815</v>
       </c>
       <c r="R31" t="n">
-        <v>6984124</v>
+        <v>6984155</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3909,19 +3915,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3948,10 +3944,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118394182</v>
+        <v>118393891</v>
       </c>
       <c r="B32" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3960,30 +3956,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>14</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3992,13 +3989,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>512007</v>
+        <v>511918</v>
       </c>
       <c r="R32" t="n">
-        <v>6984193</v>
+        <v>6984109</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4025,9 +4022,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4054,10 +4061,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118393753</v>
+        <v>118393902</v>
       </c>
       <c r="B33" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4089,7 +4096,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4098,13 +4110,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>511841</v>
+        <v>511908</v>
       </c>
       <c r="R33" t="n">
-        <v>6984146</v>
+        <v>6984095</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4131,9 +4143,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4160,10 +4182,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118394560</v>
+        <v>118393753</v>
       </c>
       <c r="B34" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4195,19 +4217,19 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>511770</v>
+        <v>511841</v>
       </c>
       <c r="R34" t="n">
-        <v>6984157</v>
+        <v>6984146</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4266,10 +4288,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118394581</v>
+        <v>118393802</v>
       </c>
       <c r="B35" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4301,19 +4323,19 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>511742</v>
+        <v>511869</v>
       </c>
       <c r="R35" t="n">
-        <v>6984149</v>
+        <v>6984157</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4372,10 +4394,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118393902</v>
+        <v>118393897</v>
       </c>
       <c r="B36" t="n">
-        <v>97846</v>
+        <v>82270</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4384,50 +4406,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>511908</v>
+        <v>511911</v>
       </c>
       <c r="R36" t="n">
-        <v>6984095</v>
+        <v>6984171</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4454,19 +4467,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4493,10 +4496,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118393135</v>
+        <v>118393108</v>
       </c>
       <c r="B37" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4505,30 +4508,31 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4537,10 +4541,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>511692</v>
+        <v>511701</v>
       </c>
       <c r="R37" t="n">
-        <v>6984065</v>
+        <v>6984061</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4599,10 +4603,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118394417</v>
+        <v>118393935</v>
       </c>
       <c r="B38" t="n">
-        <v>97846</v>
+        <v>82270</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4611,50 +4615,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>511856</v>
+        <v>511922</v>
       </c>
       <c r="R38" t="n">
-        <v>6984192</v>
+        <v>6984163</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4681,19 +4676,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4720,10 +4705,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118393044</v>
+        <v>118393818</v>
       </c>
       <c r="B39" t="n">
-        <v>82263</v>
+        <v>97853</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4732,41 +4717,50 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>511724</v>
+        <v>511903</v>
       </c>
       <c r="R39" t="n">
-        <v>6984047</v>
+        <v>6984128</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4793,9 +4787,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4822,10 +4826,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118393897</v>
+        <v>118393392</v>
       </c>
       <c r="B40" t="n">
-        <v>82263</v>
+        <v>90476</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4834,41 +4838,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>511911</v>
+        <v>511727</v>
       </c>
       <c r="R40" t="n">
-        <v>6984171</v>
+        <v>6984085</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4895,9 +4899,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4924,10 +4938,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118393392</v>
+        <v>118394901</v>
       </c>
       <c r="B41" t="n">
-        <v>90469</v>
+        <v>57290</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4936,38 +4950,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>511727</v>
+        <v>511694</v>
       </c>
       <c r="R41" t="n">
-        <v>6984085</v>
+        <v>6984128</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5036,10 +5055,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118393626</v>
+        <v>118394182</v>
       </c>
       <c r="B42" t="n">
-        <v>78484</v>
+        <v>97853</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5048,43 +5067,42 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>14</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>511824</v>
+        <v>512007</v>
       </c>
       <c r="R42" t="n">
-        <v>6984090</v>
+        <v>6984193</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5143,10 +5161,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118394327</v>
+        <v>118394560</v>
       </c>
       <c r="B43" t="n">
-        <v>90504</v>
+        <v>97853</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5155,41 +5173,45 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>511917</v>
+        <v>511770</v>
       </c>
       <c r="R43" t="n">
-        <v>6984200</v>
+        <v>6984157</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5216,19 +5238,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5255,10 +5267,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118394396</v>
+        <v>118394298</v>
       </c>
       <c r="B44" t="n">
-        <v>57290</v>
+        <v>97853</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5267,31 +5279,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5300,10 +5311,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>511862</v>
+        <v>511911</v>
       </c>
       <c r="R44" t="n">
-        <v>6984169</v>
+        <v>6984196</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5362,10 +5373,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118393726</v>
+        <v>118395009</v>
       </c>
       <c r="B45" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5395,26 +5406,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>511843</v>
+        <v>511731</v>
       </c>
       <c r="R45" t="n">
-        <v>6984124</v>
+        <v>6984133</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5483,10 +5485,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118393821</v>
+        <v>118394668</v>
       </c>
       <c r="B46" t="n">
-        <v>79565</v>
+        <v>95401</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5499,37 +5501,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>511876</v>
+        <v>511726</v>
       </c>
       <c r="R46" t="n">
-        <v>6984163</v>
+        <v>6984123</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5556,9 +5558,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5585,10 +5597,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118393472</v>
+        <v>118393346</v>
       </c>
       <c r="B47" t="n">
-        <v>97846</v>
+        <v>90865</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5601,41 +5613,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>1506</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>511752</v>
+        <v>511769</v>
       </c>
       <c r="R47" t="n">
-        <v>6984084</v>
+        <v>6984090</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5662,9 +5670,24 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Grov granlåga</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5691,10 +5714,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118393818</v>
+        <v>118394207</v>
       </c>
       <c r="B48" t="n">
-        <v>97846</v>
+        <v>74603</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5703,47 +5726,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>511903</v>
+        <v>511968</v>
       </c>
       <c r="R48" t="n">
-        <v>6984128</v>
+        <v>6984167</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5812,10 +5826,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118393781</v>
+        <v>118394396</v>
       </c>
       <c r="B49" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5824,35 +5838,31 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5861,13 +5871,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>511873</v>
+        <v>511862</v>
       </c>
       <c r="R49" t="n">
-        <v>6984099</v>
+        <v>6984169</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5894,19 +5904,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 22554-2024 artfynd.xlsx
+++ b/artfynd/A 22554-2024 artfynd.xlsx
@@ -4288,10 +4288,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118393802</v>
+        <v>118393897</v>
       </c>
       <c r="B35" t="n">
-        <v>97853</v>
+        <v>82270</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4300,42 +4300,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>511869</v>
+        <v>511911</v>
       </c>
       <c r="R35" t="n">
-        <v>6984157</v>
+        <v>6984171</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4394,10 +4390,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118393897</v>
+        <v>118393108</v>
       </c>
       <c r="B36" t="n">
-        <v>82270</v>
+        <v>57290</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4410,34 +4406,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>511911</v>
+        <v>511701</v>
       </c>
       <c r="R36" t="n">
-        <v>6984171</v>
+        <v>6984061</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4496,10 +4497,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118393108</v>
+        <v>118393802</v>
       </c>
       <c r="B37" t="n">
-        <v>57290</v>
+        <v>97853</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4508,43 +4509,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>511701</v>
+        <v>511869</v>
       </c>
       <c r="R37" t="n">
-        <v>6984061</v>
+        <v>6984157</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4826,10 +4826,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118393392</v>
+        <v>118394182</v>
       </c>
       <c r="B40" t="n">
-        <v>90476</v>
+        <v>97853</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4838,41 +4838,45 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>511727</v>
+        <v>512007</v>
       </c>
       <c r="R40" t="n">
-        <v>6984085</v>
+        <v>6984193</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4899,19 +4903,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4938,10 +4932,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118394901</v>
+        <v>118394560</v>
       </c>
       <c r="B41" t="n">
-        <v>57290</v>
+        <v>97853</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4950,31 +4944,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4983,13 +4976,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>511694</v>
+        <v>511770</v>
       </c>
       <c r="R41" t="n">
-        <v>6984128</v>
+        <v>6984157</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5016,19 +5009,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5055,10 +5038,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118394182</v>
+        <v>118393392</v>
       </c>
       <c r="B42" t="n">
-        <v>97853</v>
+        <v>90476</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5067,45 +5050,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>512007</v>
+        <v>511727</v>
       </c>
       <c r="R42" t="n">
-        <v>6984193</v>
+        <v>6984085</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5132,9 +5111,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5161,10 +5150,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118394560</v>
+        <v>118394901</v>
       </c>
       <c r="B43" t="n">
-        <v>97853</v>
+        <v>57290</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5173,30 +5162,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5205,13 +5195,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>511770</v>
+        <v>511694</v>
       </c>
       <c r="R43" t="n">
-        <v>6984157</v>
+        <v>6984128</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5238,9 +5228,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 22554-2024 artfynd.xlsx
+++ b/artfynd/A 22554-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118394590</v>
+        <v>118393753</v>
       </c>
       <c r="B2" t="n">
-        <v>57290</v>
+        <v>97853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511742</v>
+        <v>511841</v>
       </c>
       <c r="R2" t="n">
         <v>6984146</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,19 +752,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118393726</v>
+        <v>118393974</v>
       </c>
       <c r="B3" t="n">
-        <v>97853</v>
+        <v>79572</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,35 +793,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,7 +826,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511843</v>
+        <v>511892</v>
       </c>
       <c r="R3" t="n">
         <v>6984124</v>
@@ -913,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118393746</v>
+        <v>118394693</v>
       </c>
       <c r="B4" t="n">
-        <v>97853</v>
+        <v>57290</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,38 +910,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511842</v>
+        <v>511716</v>
       </c>
       <c r="R4" t="n">
-        <v>6984141</v>
+        <v>6984145</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118394693</v>
+        <v>118393902</v>
       </c>
       <c r="B5" t="n">
-        <v>57290</v>
+        <v>97853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,46 +1017,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511716</v>
+        <v>511908</v>
       </c>
       <c r="R5" t="n">
-        <v>6984145</v>
+        <v>6984095</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,9 +1087,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,7 +1126,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118395030</v>
+        <v>118393746</v>
       </c>
       <c r="B6" t="n">
         <v>97853</v>
@@ -1158,14 +1162,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511734</v>
+        <v>511842</v>
       </c>
       <c r="R6" t="n">
-        <v>6984117</v>
+        <v>6984141</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118394248</v>
+        <v>118394680</v>
       </c>
       <c r="B7" t="n">
-        <v>90511</v>
+        <v>97853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,41 +1240,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511950</v>
+        <v>511723</v>
       </c>
       <c r="R7" t="n">
-        <v>6984198</v>
+        <v>6984123</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1297,9 +1310,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118393974</v>
+        <v>118394298</v>
       </c>
       <c r="B8" t="n">
-        <v>79572</v>
+        <v>97853</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,31 +1361,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1371,13 +1393,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511892</v>
+        <v>511911</v>
       </c>
       <c r="R8" t="n">
-        <v>6984124</v>
+        <v>6984196</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1404,19 +1426,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118393821</v>
+        <v>118393108</v>
       </c>
       <c r="B9" t="n">
-        <v>79572</v>
+        <v>57290</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,34 +1471,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511876</v>
+        <v>511701</v>
       </c>
       <c r="R9" t="n">
-        <v>6984163</v>
+        <v>6984061</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,10 +1562,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118394566</v>
+        <v>118393781</v>
       </c>
       <c r="B10" t="n">
-        <v>57290</v>
+        <v>97853</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,46 +1574,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511761</v>
+        <v>511873</v>
       </c>
       <c r="R10" t="n">
-        <v>6984157</v>
+        <v>6984099</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1623,9 +1644,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118393469</v>
+        <v>118393150</v>
       </c>
       <c r="B11" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1668,42 +1699,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511791</v>
+        <v>511703</v>
       </c>
       <c r="R11" t="n">
-        <v>6984074</v>
+        <v>6984085</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1730,19 +1756,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118393135</v>
+        <v>118394550</v>
       </c>
       <c r="B12" t="n">
-        <v>97853</v>
+        <v>90529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1781,42 +1797,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511692</v>
+        <v>511801</v>
       </c>
       <c r="R12" t="n">
-        <v>6984065</v>
+        <v>6984151</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1875,10 +1887,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118393861</v>
+        <v>118393469</v>
       </c>
       <c r="B13" t="n">
-        <v>97853</v>
+        <v>57290</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1887,47 +1899,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511914</v>
+        <v>511791</v>
       </c>
       <c r="R13" t="n">
-        <v>6984121</v>
+        <v>6984074</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1996,7 +2004,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118393781</v>
+        <v>118393818</v>
       </c>
       <c r="B14" t="n">
         <v>97853</v>
@@ -2031,7 +2039,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2045,10 +2053,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511873</v>
+        <v>511903</v>
       </c>
       <c r="R14" t="n">
-        <v>6984099</v>
+        <v>6984128</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2117,10 +2125,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118394125</v>
+        <v>118393821</v>
       </c>
       <c r="B15" t="n">
-        <v>90954</v>
+        <v>79572</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2129,44 +2137,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Småmyrarna, Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>512008</v>
+        <v>511876</v>
       </c>
       <c r="R15" t="n">
-        <v>6984144</v>
+        <v>6984163</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2193,28 +2198,17 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2233,10 +2227,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118394417</v>
+        <v>118393626</v>
       </c>
       <c r="B16" t="n">
-        <v>97853</v>
+        <v>78491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2245,50 +2239,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511856</v>
+        <v>511824</v>
       </c>
       <c r="R16" t="n">
-        <v>6984192</v>
+        <v>6984090</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2315,19 +2305,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2354,10 +2334,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118393150</v>
+        <v>118393044</v>
       </c>
       <c r="B17" t="n">
-        <v>78491</v>
+        <v>82270</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2370,21 +2350,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2394,10 +2374,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511703</v>
+        <v>511724</v>
       </c>
       <c r="R17" t="n">
-        <v>6984085</v>
+        <v>6984047</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2456,10 +2436,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118394581</v>
+        <v>118393897</v>
       </c>
       <c r="B18" t="n">
-        <v>97853</v>
+        <v>82270</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2468,42 +2448,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511742</v>
+        <v>511911</v>
       </c>
       <c r="R18" t="n">
-        <v>6984149</v>
+        <v>6984171</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2562,10 +2538,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118393868</v>
+        <v>118392836</v>
       </c>
       <c r="B19" t="n">
-        <v>74595</v>
+        <v>90511</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2578,34 +2554,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511869</v>
+        <v>511716</v>
       </c>
       <c r="R19" t="n">
-        <v>6984163</v>
+        <v>6984042</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2664,10 +2640,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118392836</v>
+        <v>118394396</v>
       </c>
       <c r="B20" t="n">
-        <v>90511</v>
+        <v>57290</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2680,34 +2656,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511716</v>
+        <v>511862</v>
       </c>
       <c r="R20" t="n">
-        <v>6984042</v>
+        <v>6984169</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2766,7 +2747,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118393472</v>
+        <v>118394417</v>
       </c>
       <c r="B21" t="n">
         <v>97853</v>
@@ -2801,22 +2782,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511752</v>
+        <v>511856</v>
       </c>
       <c r="R21" t="n">
-        <v>6984084</v>
+        <v>6984192</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2843,9 +2829,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2872,7 +2868,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118393885</v>
+        <v>118394581</v>
       </c>
       <c r="B22" t="n">
         <v>97853</v>
@@ -2907,19 +2903,19 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511892</v>
+        <v>511742</v>
       </c>
       <c r="R22" t="n">
-        <v>6984185</v>
+        <v>6984149</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2978,10 +2974,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118393044</v>
+        <v>118393135</v>
       </c>
       <c r="B23" t="n">
-        <v>82270</v>
+        <v>97853</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2990,38 +2986,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>511724</v>
+        <v>511692</v>
       </c>
       <c r="R23" t="n">
-        <v>6984047</v>
+        <v>6984065</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3080,10 +3080,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118393100</v>
+        <v>118395009</v>
       </c>
       <c r="B24" t="n">
-        <v>79600</v>
+        <v>97853</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3092,25 +3092,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>511722</v>
+        <v>511731</v>
       </c>
       <c r="R24" t="n">
-        <v>6984095</v>
+        <v>6984133</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3192,10 +3192,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118393904</v>
+        <v>118394668</v>
       </c>
       <c r="B25" t="n">
-        <v>97853</v>
+        <v>95401</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3204,45 +3204,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511906</v>
+        <v>511726</v>
       </c>
       <c r="R25" t="n">
-        <v>6984171</v>
+        <v>6984123</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3269,9 +3265,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3298,10 +3304,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118394030</v>
+        <v>118394901</v>
       </c>
       <c r="B26" t="n">
-        <v>90511</v>
+        <v>57290</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3314,37 +3320,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>512003</v>
+        <v>511694</v>
       </c>
       <c r="R26" t="n">
-        <v>6984152</v>
+        <v>6984128</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3371,9 +3382,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3400,10 +3421,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118393626</v>
+        <v>118394566</v>
       </c>
       <c r="B27" t="n">
-        <v>78491</v>
+        <v>57290</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3416,27 +3437,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3445,10 +3466,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511824</v>
+        <v>511761</v>
       </c>
       <c r="R27" t="n">
-        <v>6984090</v>
+        <v>6984157</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3507,10 +3528,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118394680</v>
+        <v>118393346</v>
       </c>
       <c r="B28" t="n">
-        <v>97853</v>
+        <v>90865</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3523,43 +3544,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1506</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>511723</v>
+        <v>511769</v>
       </c>
       <c r="R28" t="n">
-        <v>6984123</v>
+        <v>6984090</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3602,6 +3614,11 @@
       <c r="AB28" t="inlineStr">
         <is>
           <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Grov granlåga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3628,10 +3645,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118394327</v>
+        <v>118394426</v>
       </c>
       <c r="B29" t="n">
-        <v>90511</v>
+        <v>79572</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3644,21 +3661,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3668,13 +3685,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511917</v>
+        <v>511815</v>
       </c>
       <c r="R29" t="n">
-        <v>6984200</v>
+        <v>6984155</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3701,19 +3718,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3740,10 +3747,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118394550</v>
+        <v>118393935</v>
       </c>
       <c r="B30" t="n">
-        <v>90529</v>
+        <v>82270</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3756,21 +3763,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3780,10 +3787,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511801</v>
+        <v>511922</v>
       </c>
       <c r="R30" t="n">
-        <v>6984151</v>
+        <v>6984163</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3842,10 +3849,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118394426</v>
+        <v>118394248</v>
       </c>
       <c r="B31" t="n">
-        <v>79572</v>
+        <v>90511</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3858,21 +3865,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3882,10 +3889,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>511815</v>
+        <v>511950</v>
       </c>
       <c r="R31" t="n">
-        <v>6984155</v>
+        <v>6984198</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3944,10 +3951,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118393891</v>
+        <v>118393904</v>
       </c>
       <c r="B32" t="n">
-        <v>57290</v>
+        <v>97853</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3956,31 +3963,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3989,13 +3995,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>511918</v>
+        <v>511906</v>
       </c>
       <c r="R32" t="n">
-        <v>6984109</v>
+        <v>6984171</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4022,19 +4028,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4061,7 +4057,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118393902</v>
+        <v>118393726</v>
       </c>
       <c r="B33" t="n">
         <v>97853</v>
@@ -4096,7 +4092,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4110,10 +4106,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>511908</v>
+        <v>511843</v>
       </c>
       <c r="R33" t="n">
-        <v>6984095</v>
+        <v>6984124</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4182,10 +4178,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118393753</v>
+        <v>118394327</v>
       </c>
       <c r="B34" t="n">
-        <v>97853</v>
+        <v>90511</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4194,45 +4190,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>511841</v>
+        <v>511917</v>
       </c>
       <c r="R34" t="n">
-        <v>6984146</v>
+        <v>6984200</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4259,9 +4251,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4288,10 +4290,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118393897</v>
+        <v>118393472</v>
       </c>
       <c r="B35" t="n">
-        <v>82270</v>
+        <v>97853</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4300,38 +4302,42 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>511911</v>
+        <v>511752</v>
       </c>
       <c r="R35" t="n">
-        <v>6984171</v>
+        <v>6984084</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4390,10 +4396,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118393108</v>
+        <v>118394030</v>
       </c>
       <c r="B36" t="n">
-        <v>57290</v>
+        <v>90511</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4406,39 +4412,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>511701</v>
+        <v>512003</v>
       </c>
       <c r="R36" t="n">
-        <v>6984061</v>
+        <v>6984152</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4497,7 +4498,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118393802</v>
+        <v>118393861</v>
       </c>
       <c r="B37" t="n">
         <v>97853</v>
@@ -4532,7 +4533,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4541,13 +4547,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>511869</v>
+        <v>511914</v>
       </c>
       <c r="R37" t="n">
-        <v>6984157</v>
+        <v>6984121</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4574,9 +4580,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4603,10 +4619,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118393935</v>
+        <v>118394560</v>
       </c>
       <c r="B38" t="n">
-        <v>82270</v>
+        <v>97853</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4615,38 +4631,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>511922</v>
+        <v>511770</v>
       </c>
       <c r="R38" t="n">
-        <v>6984163</v>
+        <v>6984157</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4705,10 +4725,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118393818</v>
+        <v>118393868</v>
       </c>
       <c r="B39" t="n">
-        <v>97853</v>
+        <v>74595</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4717,50 +4737,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>511903</v>
+        <v>511869</v>
       </c>
       <c r="R39" t="n">
-        <v>6984128</v>
+        <v>6984163</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4787,19 +4798,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4826,10 +4827,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118394182</v>
+        <v>118394207</v>
       </c>
       <c r="B40" t="n">
-        <v>97853</v>
+        <v>74603</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4838,45 +4839,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>512007</v>
+        <v>511968</v>
       </c>
       <c r="R40" t="n">
-        <v>6984193</v>
+        <v>6984167</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4903,9 +4900,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4932,10 +4939,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118394560</v>
+        <v>118393100</v>
       </c>
       <c r="B41" t="n">
-        <v>97853</v>
+        <v>79600</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4944,45 +4951,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>511770</v>
+        <v>511722</v>
       </c>
       <c r="R41" t="n">
-        <v>6984157</v>
+        <v>6984095</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5009,9 +5012,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5038,10 +5051,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118393392</v>
+        <v>118394125</v>
       </c>
       <c r="B42" t="n">
-        <v>90476</v>
+        <v>90954</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5050,41 +5063,44 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>511727</v>
+        <v>512008</v>
       </c>
       <c r="R42" t="n">
-        <v>6984085</v>
+        <v>6984144</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5132,6 +5148,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5150,7 +5167,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118394901</v>
+        <v>118393891</v>
       </c>
       <c r="B43" t="n">
         <v>57290</v>
@@ -5186,19 +5203,19 @@
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>511694</v>
+        <v>511918</v>
       </c>
       <c r="R43" t="n">
-        <v>6984128</v>
+        <v>6984109</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5267,7 +5284,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118394298</v>
+        <v>118395030</v>
       </c>
       <c r="B44" t="n">
         <v>97853</v>
@@ -5300,21 +5317,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>511911</v>
+        <v>511734</v>
       </c>
       <c r="R44" t="n">
-        <v>6984196</v>
+        <v>6984117</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5373,7 +5386,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118395009</v>
+        <v>118393885</v>
       </c>
       <c r="B45" t="n">
         <v>97853</v>
@@ -5406,20 +5419,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>511731</v>
+        <v>511892</v>
       </c>
       <c r="R45" t="n">
-        <v>6984133</v>
+        <v>6984185</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5446,19 +5463,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5485,10 +5492,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118394668</v>
+        <v>118393802</v>
       </c>
       <c r="B46" t="n">
-        <v>95401</v>
+        <v>97853</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5497,41 +5504,45 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>511726</v>
+        <v>511869</v>
       </c>
       <c r="R46" t="n">
-        <v>6984123</v>
+        <v>6984157</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5558,19 +5569,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5597,10 +5598,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118393346</v>
+        <v>118394182</v>
       </c>
       <c r="B47" t="n">
-        <v>90865</v>
+        <v>97853</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5613,37 +5614,41 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1506</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
+          <t>Småmyrarna (Småmyrarna), Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>511769</v>
+        <v>512007</v>
       </c>
       <c r="R47" t="n">
-        <v>6984090</v>
+        <v>6984193</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5670,24 +5675,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Grov granlåga</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5714,10 +5704,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118394207</v>
+        <v>118394590</v>
       </c>
       <c r="B48" t="n">
-        <v>74603</v>
+        <v>57290</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5730,34 +5720,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>511968</v>
+        <v>511742</v>
       </c>
       <c r="R48" t="n">
-        <v>6984167</v>
+        <v>6984146</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5826,10 +5821,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118394396</v>
+        <v>118393392</v>
       </c>
       <c r="B49" t="n">
-        <v>57290</v>
+        <v>90476</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5838,46 +5833,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Småmyrarna (Småmyrarna), Jmt</t>
+          <t>Bodtjärnen (Bodtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>511862</v>
+        <v>511727</v>
       </c>
       <c r="R49" t="n">
-        <v>6984169</v>
+        <v>6984085</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5904,9 +5894,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD49" t="b">
